--- a/data/credit_bond_all_2026-10-20.xlsx
+++ b/data/credit_bond_all_2026-10-20.xlsx
@@ -1645,8 +1645,12 @@
           <t>1.40 ~ 2.40</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>61.47</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>1.87</t>
@@ -17857,8 +17861,12 @@
           <t>1.30 ~ 1.90</t>
         </is>
       </c>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
+      <c r="H77" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>15.47</v>
+      </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
